--- a/pedidos/F2026017S.xlsx
+++ b/pedidos/F2026017S.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Agroserver\gestao_projetos\08_Processo_Químico\02_Clientes\OS_2026\ATVOS\OS_017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Agroserver\libs_analise\01_Comerciais\05) ATVOS\2026-07-17 - Remessa17\07_Referencias_Quimico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE29C41-6431-4DF6-A841-2B87B07B971E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8655EF4-B403-42D8-8FA4-2157D58EFD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BI$45</definedName>
+  </definedNames>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -208,220 +216,220 @@
     <t>6/22/202615:00:00</t>
   </si>
   <si>
+    <t>PRESIDENTE_EPITACIO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>UCP_FERTILIDADE</t>
+  </si>
+  <si>
+    <t>UCP</t>
+  </si>
+  <si>
+    <t>00-25</t>
+  </si>
+  <si>
+    <t>Fertilidade</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260556</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>25-50</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S261405</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260557</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260555</t>
+  </si>
+  <si>
     <t>6/22/202615:00:01</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260559</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260558</t>
+  </si>
+  <si>
     <t>6/22/202615:00:02</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260561</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260560</t>
+  </si>
+  <si>
     <t>6/22/202615:00:03</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260553</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260551</t>
+  </si>
+  <si>
     <t>6/22/202615:00:04</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S261404</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260562</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260545</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260547</t>
+  </si>
+  <si>
     <t>6/22/202614:28:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260548</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260531</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260550</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260549</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260552</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260546</t>
+  </si>
+  <si>
     <t>6/22/202616:29:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260536</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260537</t>
+  </si>
+  <si>
     <t>6/22/202615:37:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260533</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260534</t>
+  </si>
+  <si>
     <t>6/26/202612:14:00</t>
   </si>
   <si>
+    <t>MARABA_PAULISTA</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260878</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260879</t>
+  </si>
+  <si>
     <t>6/26/202612:45:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260876</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260877</t>
+  </si>
+  <si>
     <t>6/26/202613:08:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260874</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260875</t>
+  </si>
+  <si>
     <t>6/26/202613:27:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260870</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260871</t>
+  </si>
+  <si>
     <t>6/26/202613:20:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260872</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260873</t>
+  </si>
+  <si>
     <t>6/23/202613:02:00</t>
   </si>
   <si>
+    <t>MIRANTE_DO_PARANAPANEMA</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260535</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260539</t>
+  </si>
+  <si>
     <t>6/24/202612:56:00</t>
   </si>
   <si>
+    <t>TEODORO_SAMPAIO</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260569</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260568</t>
+  </si>
+  <si>
     <t>6/24/202612:29:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260571</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260570</t>
+  </si>
+  <si>
     <t>6/24/202612:06:00</t>
   </si>
   <si>
+    <t>ASP26010200000118A11S260532</t>
+  </si>
+  <si>
+    <t>ASP26010200000118A11S260540</t>
+  </si>
+  <si>
     <t>6/24/202611:48:00</t>
   </si>
   <si>
-    <t>PRESIDENTE_EPITACIO</t>
-  </si>
-  <si>
-    <t>MARABA_PAULISTA</t>
-  </si>
-  <si>
-    <t>MIRANTE_DO_PARANAPANEMA</t>
-  </si>
-  <si>
-    <t>TEODORO_SAMPAIO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>UCP_FERTILIDADE</t>
-  </si>
-  <si>
-    <t>UCP</t>
-  </si>
-  <si>
-    <t>00-25</t>
-  </si>
-  <si>
-    <t>25-50</t>
-  </si>
-  <si>
-    <t>Fertilidade</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260556</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S261405</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260557</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260555</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260559</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260558</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260561</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260560</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260553</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260551</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S261404</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260562</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260545</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260547</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260548</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260531</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260550</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260549</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260552</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260546</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260536</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260537</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260533</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260534</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260878</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260879</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260876</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260877</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260874</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260875</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260870</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260871</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260872</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260873</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260535</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260539</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260569</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260568</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260571</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260570</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260532</t>
-  </si>
-  <si>
-    <t>ASP26010200000118A11S260540</t>
-  </si>
-  <si>
     <t>ASP26010200000118A11S260573</t>
   </si>
   <si>
     <t>ASP26010200000118A11S260572</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
 </sst>
 </file>
@@ -431,18 +439,18 @@
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -490,7 +498,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -503,9 +511,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -513,44 +521,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -578,14 +586,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -613,9 +638,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -624,234 +666,229 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" customWidth="1"/>
+    <col min="20" max="20" width="6.28515625" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" customWidth="1"/>
+    <col min="24" max="24" width="29.28515625" customWidth="1"/>
+    <col min="25" max="25" width="3.85546875" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" customWidth="1"/>
+    <col min="29" max="29" width="6.5703125" customWidth="1"/>
+    <col min="30" max="30" width="6.140625" customWidth="1"/>
+    <col min="31" max="31" width="4.28515625" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" customWidth="1"/>
+    <col min="34" max="34" width="9" customWidth="1"/>
+    <col min="35" max="35" width="5.85546875" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" customWidth="1"/>
+    <col min="38" max="38" width="6.140625" customWidth="1"/>
+    <col min="39" max="39" width="11.85546875" customWidth="1"/>
+    <col min="40" max="40" width="18.7109375" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" customWidth="1"/>
+    <col min="43" max="43" width="12" customWidth="1"/>
+    <col min="44" max="44" width="16.140625" customWidth="1"/>
+    <col min="45" max="45" width="16.42578125" customWidth="1"/>
+    <col min="46" max="46" width="15.42578125" customWidth="1"/>
+    <col min="47" max="47" width="17.28515625" customWidth="1"/>
+    <col min="48" max="48" width="16.7109375" customWidth="1"/>
+    <col min="49" max="49" width="12" customWidth="1"/>
+    <col min="50" max="50" width="13.28515625" customWidth="1"/>
+    <col min="51" max="51" width="13.140625" customWidth="1"/>
+    <col min="52" max="52" width="14" customWidth="1"/>
+    <col min="53" max="53" width="13.140625" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" customWidth="1"/>
+    <col min="55" max="55" width="7.5703125" customWidth="1"/>
+    <col min="57" max="57" width="7.85546875" customWidth="1"/>
+    <col min="58" max="58" width="18.5703125" customWidth="1"/>
+    <col min="59" max="59" width="12" customWidth="1"/>
+    <col min="60" max="60" width="12.42578125" customWidth="1"/>
+    <col min="61" max="61" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.25">
@@ -1041,25 +1078,25 @@
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B2">
-        <v>-52.332361459535832</v>
+        <v>-52.332361459535797</v>
       </c>
       <c r="C2">
-        <v>-22.235503863438851</v>
+        <v>-22.2355038634389</v>
       </c>
       <c r="D2" t="s">
         <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1071,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O2">
         <v>120102</v>
@@ -1089,54 +1126,87 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X2" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
       <c r="AC2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI2" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM2">
+        <v>0.65</v>
+      </c>
+      <c r="AN2">
+        <v>6.6103948304115301</v>
+      </c>
+      <c r="AR2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AS2">
+        <v>13.55</v>
+      </c>
+      <c r="AT2">
+        <v>1.83</v>
+      </c>
+      <c r="AU2">
+        <v>7.61</v>
+      </c>
+      <c r="BB2">
+        <v>11.1820633863666</v>
+      </c>
+      <c r="BD2">
+        <v>6.15</v>
+      </c>
+      <c r="BE2">
+        <v>7.41</v>
+      </c>
+      <c r="BF2">
+        <v>9.5544679993040305</v>
       </c>
     </row>
     <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B3">
-        <v>-52.332361459535832</v>
+        <v>-52.332361459535797</v>
       </c>
       <c r="C3">
-        <v>-22.235503863438851</v>
+        <v>-22.2355038634389</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1148,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O3">
         <v>120102</v>
@@ -1166,54 +1236,87 @@
         <v>2</v>
       </c>
       <c r="V3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="Y3">
         <v>2</v>
       </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
       <c r="AC3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI3" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM3">
+        <v>0.54</v>
+      </c>
+      <c r="AN3">
+        <v>5.4460006802090097</v>
+      </c>
+      <c r="AR3">
+        <v>0.86</v>
+      </c>
+      <c r="AS3">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AT3">
+        <v>1.88</v>
+      </c>
+      <c r="AU3">
+        <v>5.59</v>
+      </c>
+      <c r="BB3">
+        <v>9.7336052239457107</v>
+      </c>
+      <c r="BD3">
+        <v>6</v>
+      </c>
+      <c r="BE3">
+        <v>7.38</v>
+      </c>
+      <c r="BF3">
+        <v>9.8613186639896302</v>
       </c>
     </row>
     <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B4">
-        <v>-52.328525036776647</v>
+        <v>-52.328525036776703</v>
       </c>
       <c r="C4">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1225,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O4">
         <v>120102</v>
@@ -1243,54 +1346,87 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W4" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X4" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="Y4">
         <v>3</v>
       </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
       <c r="AC4" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE4" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF4" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH4" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI4" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM4">
+        <v>0.62</v>
+      </c>
+      <c r="AN4">
+        <v>6.9430788733265301</v>
+      </c>
+      <c r="AR4">
+        <v>0.69</v>
+      </c>
+      <c r="AS4">
+        <v>10.25</v>
+      </c>
+      <c r="AT4">
+        <v>0.97</v>
+      </c>
+      <c r="AU4">
+        <v>4.88</v>
+      </c>
+      <c r="BB4">
+        <v>9.3714906833404896</v>
+      </c>
+      <c r="BD4">
+        <v>6.03</v>
+      </c>
+      <c r="BE4">
+        <v>7.51</v>
+      </c>
+      <c r="BF4">
+        <v>8.5989396437009606</v>
       </c>
     </row>
     <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B5">
-        <v>-52.328525036776647</v>
+        <v>-52.328525036776703</v>
       </c>
       <c r="C5">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1302,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O5">
         <v>120102</v>
@@ -1320,51 +1456,81 @@
         <v>2</v>
       </c>
       <c r="V5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W5" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X5" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="Y5">
         <v>4</v>
       </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
       <c r="AC5" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF5" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH5" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI5" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM5">
+        <v>0.87</v>
+      </c>
+      <c r="AN5">
+        <v>7.9411310020715504</v>
+      </c>
+      <c r="AR5">
+        <v>0.94</v>
+      </c>
+      <c r="AS5">
+        <v>10.72</v>
+      </c>
+      <c r="AT5">
+        <v>1.58</v>
+      </c>
+      <c r="AU5">
+        <v>5.07</v>
+      </c>
+      <c r="BD5">
+        <v>6.35</v>
+      </c>
+      <c r="BE5">
+        <v>7.53</v>
+      </c>
+      <c r="BF5">
+        <v>8.4196216992408992</v>
       </c>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B6">
-        <v>-52.325189433400418</v>
+        <v>-52.325189433400404</v>
       </c>
       <c r="C6">
-        <v>-22.236395855898341</v>
+        <v>-22.236395855898301</v>
       </c>
       <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" t="s">
         <v>62</v>
       </c>
-      <c r="F6" t="s">
-        <v>79</v>
-      </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1376,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O6">
         <v>120102</v>
@@ -1394,51 +1560,81 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X6" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="Y6">
         <v>5</v>
       </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
       <c r="AC6" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF6" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH6" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI6" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM6">
+        <v>0.73</v>
+      </c>
+      <c r="AN6">
+        <v>9.4382091951890708</v>
+      </c>
+      <c r="AR6">
+        <v>0.67</v>
+      </c>
+      <c r="AS6">
+        <v>22.01</v>
+      </c>
+      <c r="AT6">
+        <v>0.87</v>
+      </c>
+      <c r="AU6">
+        <v>4.32</v>
+      </c>
+      <c r="BD6">
+        <v>6.79</v>
+      </c>
+      <c r="BE6">
+        <v>7.67</v>
+      </c>
+      <c r="BF6">
+        <v>7.2648445407719198</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>-52.325189433400418</v>
+        <v>-52.325189433400404</v>
       </c>
       <c r="C7">
-        <v>-22.236395855898341</v>
+        <v>-22.236395855898301</v>
       </c>
       <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" t="s">
         <v>62</v>
       </c>
-      <c r="F7" t="s">
-        <v>79</v>
-      </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1450,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O7">
         <v>120102</v>
@@ -1468,51 +1664,81 @@
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W7" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="Y7">
         <v>6</v>
       </c>
+      <c r="Z7">
+        <v>6</v>
+      </c>
       <c r="AC7" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF7" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH7" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI7" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AN7">
+        <v>6.1113687660390204</v>
+      </c>
+      <c r="AR7">
+        <v>1.03</v>
+      </c>
+      <c r="AS7">
+        <v>10.78</v>
+      </c>
+      <c r="AT7">
+        <v>0.82</v>
+      </c>
+      <c r="AU7">
+        <v>3.51</v>
+      </c>
+      <c r="BD7">
+        <v>6.42</v>
+      </c>
+      <c r="BE7">
+        <v>7.62</v>
+      </c>
+      <c r="BF7">
+        <v>7.6578548467314898</v>
       </c>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>-52.324022115706057</v>
+        <v>-52.3240221157061</v>
       </c>
       <c r="C8">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
         <v>63</v>
       </c>
-      <c r="F8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" t="s">
-        <v>83</v>
-      </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1524,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O8">
         <v>120102</v>
@@ -1542,51 +1768,81 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W8" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X8" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="Y8">
         <v>7</v>
       </c>
+      <c r="Z8">
+        <v>7</v>
+      </c>
       <c r="AC8" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF8" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH8" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI8" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM8">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="AN8">
+        <v>11.101629409764101</v>
+      </c>
+      <c r="AR8">
+        <v>0.59</v>
+      </c>
+      <c r="AS8">
+        <v>11.21</v>
+      </c>
+      <c r="AT8">
+        <v>0.54</v>
+      </c>
+      <c r="AU8">
+        <v>5.24</v>
+      </c>
+      <c r="BD8">
+        <v>6.4</v>
+      </c>
+      <c r="BE8">
+        <v>7.65</v>
+      </c>
+      <c r="BF8">
+        <v>7.4195684745076402</v>
       </c>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>-52.324022115706057</v>
+        <v>-52.3240221157061</v>
       </c>
       <c r="C9">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" t="s">
-        <v>83</v>
-      </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1598,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O9">
         <v>120102</v>
@@ -1616,52 +1872,82 @@
         <v>2</v>
       </c>
       <c r="V9" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W9" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X9" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="Y9">
         <v>8</v>
       </c>
+      <c r="Z9">
+        <v>8</v>
+      </c>
       <c r="AC9" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF9" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH9" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI9" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM9">
+        <v>1.17</v>
+      </c>
+      <c r="AN9">
+        <v>37.716352842964497</v>
+      </c>
+      <c r="AR9">
+        <v>0.67</v>
+      </c>
+      <c r="AS9">
+        <v>11.39</v>
+      </c>
+      <c r="AT9">
+        <v>0.72</v>
+      </c>
+      <c r="AU9">
+        <v>5.28</v>
+      </c>
+      <c r="BD9">
+        <v>6.18</v>
+      </c>
+      <c r="BE9">
+        <v>7.55</v>
+      </c>
+      <c r="BF9">
+        <v>8.2440431606305893</v>
       </c>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B10">
-        <v>-52.319519194635447</v>
+        <v>-52.319519194635497</v>
       </c>
       <c r="C10">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>84</v>
-      </c>
       <c r="J10">
         <v>1</v>
       </c>
@@ -1672,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O10">
         <v>120102</v>
@@ -1690,52 +1976,82 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W10" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X10" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="Y10">
         <v>9</v>
       </c>
+      <c r="Z10">
+        <v>9</v>
+      </c>
       <c r="AC10" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF10" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH10" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI10" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM10">
+        <v>1.21</v>
+      </c>
+      <c r="AN10">
+        <v>6.2777107874965203</v>
+      </c>
+      <c r="AR10">
+        <v>0.75</v>
+      </c>
+      <c r="AS10">
+        <v>12.04</v>
+      </c>
+      <c r="AT10">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AU10">
+        <v>5.61</v>
+      </c>
+      <c r="BD10">
+        <v>5.82</v>
+      </c>
+      <c r="BE10">
+        <v>7.39</v>
+      </c>
+      <c r="BF10">
+        <v>9.7579554745428698</v>
       </c>
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B11">
-        <v>-52.319519194635447</v>
+        <v>-52.319519194635497</v>
       </c>
       <c r="C11">
-        <v>-22.232891190057931</v>
+        <v>-22.232891190057899</v>
       </c>
       <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
         <v>64</v>
       </c>
-      <c r="F11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>84</v>
-      </c>
       <c r="J11">
         <v>1</v>
       </c>
@@ -1746,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O11">
         <v>120102</v>
@@ -1764,63 +2080,93 @@
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W11" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="Y11">
         <v>10</v>
       </c>
+      <c r="Z11">
+        <v>10</v>
+      </c>
       <c r="AC11" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF11" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH11" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI11" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM11">
+        <v>1.34</v>
+      </c>
+      <c r="AN11">
+        <v>7.2757629162415398</v>
+      </c>
+      <c r="AR11">
+        <v>0.52</v>
+      </c>
+      <c r="AS11">
+        <v>9.31</v>
+      </c>
+      <c r="AT11">
+        <v>0.98</v>
+      </c>
+      <c r="AU11">
+        <v>4.87</v>
+      </c>
+      <c r="BD11">
+        <v>5.76</v>
+      </c>
+      <c r="BE11">
+        <v>7.44</v>
+      </c>
+      <c r="BF11">
+        <v>9.2571654826528</v>
       </c>
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B12">
-        <v>-52.324022115705993</v>
+        <v>-52.324022115706001</v>
       </c>
       <c r="C12">
-        <v>-22.228439255534489</v>
+        <v>-22.2284392555345</v>
       </c>
       <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
         <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>85</v>
       </c>
       <c r="O12">
         <v>120102</v>
@@ -1838,63 +2184,93 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W12" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X12" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="Y12">
         <v>11</v>
       </c>
+      <c r="Z12">
+        <v>11</v>
+      </c>
       <c r="AC12" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF12" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH12" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI12" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM12">
+        <v>1.73</v>
+      </c>
+      <c r="AN12">
+        <v>6.6103948304115301</v>
+      </c>
+      <c r="AR12">
+        <v>0.19</v>
+      </c>
+      <c r="AS12">
+        <v>10.61</v>
+      </c>
+      <c r="AT12">
+        <v>0.64</v>
+      </c>
+      <c r="AU12">
+        <v>5.23</v>
+      </c>
+      <c r="BD12">
+        <v>6.5</v>
+      </c>
+      <c r="BE12">
+        <v>7.6</v>
+      </c>
+      <c r="BF12">
+        <v>7.8209489665318204</v>
       </c>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>-52.324022115705993</v>
+        <v>-52.324022115706001</v>
       </c>
       <c r="C13">
-        <v>-22.228439255534489</v>
+        <v>-22.2284392555345</v>
       </c>
       <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
         <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>85</v>
       </c>
       <c r="O13">
         <v>120102</v>
@@ -1912,28 +2288,58 @@
         <v>2</v>
       </c>
       <c r="V13" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W13" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Y13">
         <v>12</v>
       </c>
+      <c r="Z13">
+        <v>12</v>
+      </c>
       <c r="AC13" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF13" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH13" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI13" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM13">
+        <v>1.6</v>
+      </c>
+      <c r="AN13">
+        <v>7.9411310020715504</v>
+      </c>
+      <c r="AR13">
+        <v>0.02</v>
+      </c>
+      <c r="AS13">
+        <v>7.47</v>
+      </c>
+      <c r="AT13">
+        <v>0.61</v>
+      </c>
+      <c r="AU13">
+        <v>4.53</v>
+      </c>
+      <c r="BD13">
+        <v>6.15</v>
+      </c>
+      <c r="BE13">
+        <v>7.41</v>
+      </c>
+      <c r="BF13">
+        <v>9.5544679993040305</v>
       </c>
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.25">
@@ -1941,25 +2347,25 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>-52.315670752553963</v>
+        <v>-52.315670752553999</v>
       </c>
       <c r="C14">
-        <v>-22.22869425066817</v>
+        <v>-22.228694250668202</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1971,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O14">
         <v>120102</v>
@@ -1989,31 +2395,64 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
+        <v>66</v>
+      </c>
+      <c r="W14" t="s">
+        <v>67</v>
+      </c>
+      <c r="X14" t="s">
         <v>86</v>
-      </c>
-      <c r="W14" t="s">
-        <v>88</v>
-      </c>
-      <c r="X14" t="s">
-        <v>101</v>
       </c>
       <c r="Y14">
         <v>13</v>
       </c>
+      <c r="Z14">
+        <v>13</v>
+      </c>
       <c r="AC14" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE14" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF14" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH14" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI14" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>6.7767368518690301</v>
+      </c>
+      <c r="AR14">
+        <v>0.09</v>
+      </c>
+      <c r="AS14">
+        <v>7.83</v>
+      </c>
+      <c r="AT14">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AU14">
+        <v>3.71</v>
+      </c>
+      <c r="BB14">
+        <v>7.5609179803143496</v>
+      </c>
+      <c r="BD14">
+        <v>6.18</v>
+      </c>
+      <c r="BE14">
+        <v>7.54</v>
+      </c>
+      <c r="BF14">
+        <v>8.3313699164497503</v>
       </c>
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.25">
@@ -2021,25 +2460,25 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>-52.315670752553963</v>
+        <v>-52.315670752553999</v>
       </c>
       <c r="C15">
-        <v>-22.22869425066817</v>
+        <v>-22.228694250668202</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2051,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O15">
         <v>120102</v>
@@ -2069,28 +2508,58 @@
         <v>2</v>
       </c>
       <c r="V15" t="s">
+        <v>70</v>
+      </c>
+      <c r="W15" t="s">
+        <v>67</v>
+      </c>
+      <c r="X15" t="s">
         <v>87</v>
-      </c>
-      <c r="W15" t="s">
-        <v>88</v>
-      </c>
-      <c r="X15" t="s">
-        <v>102</v>
       </c>
       <c r="Y15">
         <v>14</v>
       </c>
+      <c r="Z15">
+        <v>14</v>
+      </c>
       <c r="AC15" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF15" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH15" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI15" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM15">
+        <v>0.84</v>
+      </c>
+      <c r="AN15">
+        <v>7.7747889806140504</v>
+      </c>
+      <c r="AR15">
+        <v>0.04</v>
+      </c>
+      <c r="AS15">
+        <v>9.9</v>
+      </c>
+      <c r="AT15">
+        <v>0.83</v>
+      </c>
+      <c r="AU15">
+        <v>4.18</v>
+      </c>
+      <c r="BD15">
+        <v>6.26</v>
+      </c>
+      <c r="BE15">
+        <v>7.58</v>
+      </c>
+      <c r="BF15">
+        <v>7.98751660371342</v>
       </c>
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.25">
@@ -2098,25 +2567,25 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>-52.319476105495433</v>
+        <v>-52.319476105495397</v>
       </c>
       <c r="C16">
-        <v>-22.223211716490351</v>
+        <v>-22.2232117164904</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2128,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O16">
         <v>120102</v>
@@ -2146,54 +2615,84 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W16" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="Y16">
         <v>15</v>
       </c>
+      <c r="Z16">
+        <v>15</v>
+      </c>
       <c r="AC16" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF16" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH16" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI16" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM16">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AN16">
+        <v>11.6006554741366</v>
+      </c>
+      <c r="AR16">
+        <v>0.02</v>
+      </c>
+      <c r="AS16">
+        <v>13.8</v>
+      </c>
+      <c r="AT16">
+        <v>0.79</v>
+      </c>
+      <c r="AU16">
+        <v>5.83</v>
+      </c>
+      <c r="BD16">
+        <v>6.42</v>
+      </c>
+      <c r="BE16">
+        <v>7.56</v>
+      </c>
+      <c r="BF16">
+        <v>8.1576317359464703</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17">
-        <v>-52.319476105495433</v>
+        <v>-52.319476105495397</v>
       </c>
       <c r="C17">
-        <v>-22.223211716490351</v>
+        <v>-22.2232117164904</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2205,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O17">
         <v>120102</v>
@@ -2223,54 +2722,84 @@
         <v>2</v>
       </c>
       <c r="V17" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W17" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X17" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="Y17">
         <v>16</v>
       </c>
+      <c r="Z17">
+        <v>16</v>
+      </c>
       <c r="AC17" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF17" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH17" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI17" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM17">
+        <v>1.27</v>
+      </c>
+      <c r="AN17">
+        <v>22.2465448474168</v>
+      </c>
+      <c r="AR17">
+        <v>0.05</v>
+      </c>
+      <c r="AS17">
+        <v>10.17</v>
+      </c>
+      <c r="AT17">
+        <v>0.89</v>
+      </c>
+      <c r="AU17">
+        <v>4.66</v>
+      </c>
+      <c r="BD17">
+        <v>6.03</v>
+      </c>
+      <c r="BE17">
+        <v>7.35</v>
+      </c>
+      <c r="BF17">
+        <v>10.1780241244027</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18">
-        <v>-52.315016273564872</v>
+        <v>-52.3150162735649</v>
       </c>
       <c r="C18">
-        <v>-22.223987321011009</v>
+        <v>-22.223987321010998</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2282,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O18">
         <v>120102</v>
@@ -2300,54 +2829,84 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W18" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X18" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="Y18">
         <v>17</v>
       </c>
+      <c r="Z18">
+        <v>17</v>
+      </c>
       <c r="AC18" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF18" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH18" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI18" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM18">
+        <v>1.19</v>
+      </c>
+      <c r="AN18">
+        <v>9.4382091951890708</v>
+      </c>
+      <c r="AR18">
+        <v>0.03</v>
+      </c>
+      <c r="AS18">
+        <v>11.93</v>
+      </c>
+      <c r="AT18">
+        <v>1.6</v>
+      </c>
+      <c r="AU18">
+        <v>4.72</v>
+      </c>
+      <c r="BD18">
+        <v>6.29</v>
+      </c>
+      <c r="BE18">
+        <v>7.51</v>
+      </c>
+      <c r="BF18">
+        <v>8.5989396437009606</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
       <c r="B19">
-        <v>-52.315016273564872</v>
+        <v>-52.3150162735649</v>
       </c>
       <c r="C19">
-        <v>-22.223987321011009</v>
+        <v>-22.223987321010998</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2359,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O19">
         <v>120102</v>
@@ -2377,54 +2936,84 @@
         <v>2</v>
       </c>
       <c r="V19" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W19" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X19" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="Y19">
         <v>18</v>
       </c>
+      <c r="Z19">
+        <v>18</v>
+      </c>
       <c r="AC19" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF19" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH19" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI19" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM19">
+        <v>1.04</v>
+      </c>
+      <c r="AN19">
+        <v>5.6123427016665097</v>
+      </c>
+      <c r="AR19">
+        <v>0.06</v>
+      </c>
+      <c r="AS19">
+        <v>7.06</v>
+      </c>
+      <c r="AT19">
+        <v>1.04</v>
+      </c>
+      <c r="AU19">
+        <v>3.53</v>
+      </c>
+      <c r="BD19">
+        <v>5.99</v>
+      </c>
+      <c r="BE19">
+        <v>7.5</v>
+      </c>
+      <c r="BF19">
+        <v>8.6900257149329896</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
       <c r="B20">
-        <v>-52.310513352494283</v>
+        <v>-52.310513352494297</v>
       </c>
       <c r="C20">
-        <v>-22.223987321011009</v>
+        <v>-22.223987321010998</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2436,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O20">
         <v>120102</v>
@@ -2454,54 +3043,84 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W20" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="Y20">
         <v>19</v>
       </c>
+      <c r="Z20">
+        <v>19</v>
+      </c>
       <c r="AC20" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF20" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH20" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI20" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM20">
+        <v>1.48</v>
+      </c>
+      <c r="AN20">
+        <v>29.898277834461901</v>
+      </c>
+      <c r="AR20">
+        <v>0.05</v>
+      </c>
+      <c r="AS20">
+        <v>12.94</v>
+      </c>
+      <c r="AT20">
+        <v>0.91</v>
+      </c>
+      <c r="AU20">
+        <v>6.05</v>
+      </c>
+      <c r="BD20">
+        <v>6.14</v>
+      </c>
+      <c r="BE20">
+        <v>7.44</v>
+      </c>
+      <c r="BF20">
+        <v>9.2571654826528</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>16</v>
       </c>
       <c r="B21">
-        <v>-52.310513352494283</v>
+        <v>-52.310513352494297</v>
       </c>
       <c r="C21">
-        <v>-22.223987321011009</v>
+        <v>-22.223987321010998</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2513,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O21">
         <v>120102</v>
@@ -2531,31 +3150,61 @@
         <v>2</v>
       </c>
       <c r="V21" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W21" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X21" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="Y21">
         <v>20</v>
       </c>
+      <c r="Z21">
+        <v>20</v>
+      </c>
       <c r="AC21" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF21" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH21" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI21" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM21">
+        <v>1.65</v>
+      </c>
+      <c r="AN21">
+        <v>12.9313916457966</v>
+      </c>
+      <c r="AR21">
+        <v>0.04</v>
+      </c>
+      <c r="AS21">
+        <v>17.27</v>
+      </c>
+      <c r="AT21">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AU21">
+        <v>7.52</v>
+      </c>
+      <c r="BD21">
+        <v>6.41</v>
+      </c>
+      <c r="BE21">
+        <v>7.5</v>
+      </c>
+      <c r="BF21">
+        <v>8.6900257149329896</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>13</v>
       </c>
@@ -2563,22 +3212,22 @@
         <v>-52.310673312088902</v>
       </c>
       <c r="C22">
-        <v>-22.219855305677051</v>
+        <v>-22.2198553056771</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2590,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O22">
         <v>120102</v>
@@ -2608,34 +3257,67 @@
         <v>1</v>
       </c>
       <c r="V22" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W22" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X22" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="Y22">
         <v>21</v>
       </c>
+      <c r="Z22">
+        <v>21</v>
+      </c>
       <c r="AC22" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE22" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF22" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH22" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI22" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM22">
+        <v>1.41</v>
+      </c>
+      <c r="AN22">
+        <v>10.103577281019099</v>
+      </c>
+      <c r="AR22">
+        <v>0.4</v>
+      </c>
+      <c r="AS22">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="AT22">
+        <v>1.21</v>
+      </c>
+      <c r="AU22">
+        <v>5.9</v>
+      </c>
+      <c r="BB22">
+        <v>12.8115788190901</v>
+      </c>
+      <c r="BD22">
+        <v>6.3</v>
+      </c>
+      <c r="BE22">
+        <v>7.4</v>
+      </c>
+      <c r="BF22">
+        <v>9.6556757050013502</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>13</v>
       </c>
@@ -2643,22 +3325,22 @@
         <v>-52.310673312088902</v>
       </c>
       <c r="C23">
-        <v>-22.219855305677051</v>
+        <v>-22.2198553056771</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2670,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O23">
         <v>120102</v>
@@ -2688,54 +3370,84 @@
         <v>2</v>
       </c>
       <c r="V23" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W23" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X23" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="Y23">
         <v>22</v>
       </c>
+      <c r="Z23">
+        <v>22</v>
+      </c>
       <c r="AC23" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF23" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH23" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI23" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM23">
+        <v>1.6</v>
+      </c>
+      <c r="AN23">
+        <v>8.1074730235290495</v>
+      </c>
+      <c r="AR23">
+        <v>0.46</v>
+      </c>
+      <c r="AS23">
+        <v>15.81</v>
+      </c>
+      <c r="AT23">
+        <v>2.76</v>
+      </c>
+      <c r="AU23">
+        <v>6.8</v>
+      </c>
+      <c r="BD23">
+        <v>6.21</v>
+      </c>
+      <c r="BE23">
+        <v>7.41</v>
+      </c>
+      <c r="BF23">
+        <v>9.5544679993040305</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>12</v>
       </c>
       <c r="B24">
-        <v>-52.314784889920411</v>
+        <v>-52.314784889920404</v>
       </c>
       <c r="C24">
-        <v>-22.219030469033932</v>
+        <v>-22.2190304690339</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2747,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O24">
         <v>120102</v>
@@ -2765,54 +3477,84 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W24" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X24" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y24">
         <v>23</v>
       </c>
+      <c r="Z24">
+        <v>23</v>
+      </c>
       <c r="AC24" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF24" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH24" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI24" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM24">
+        <v>1.6</v>
+      </c>
+      <c r="AN24">
+        <v>56.180317224747199</v>
+      </c>
+      <c r="AR24">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AS24">
+        <v>10.61</v>
+      </c>
+      <c r="AT24">
+        <v>1.21</v>
+      </c>
+      <c r="AU24">
+        <v>4.74</v>
+      </c>
+      <c r="BD24">
+        <v>5.92</v>
+      </c>
+      <c r="BE24">
+        <v>7.24</v>
+      </c>
+      <c r="BF24">
+        <v>11.4288161488497</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
       <c r="B25">
-        <v>-52.314784889920411</v>
+        <v>-52.314784889920404</v>
       </c>
       <c r="C25">
-        <v>-22.219030469033932</v>
+        <v>-22.2190304690339</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2824,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O25">
         <v>120102</v>
@@ -2842,54 +3584,84 @@
         <v>2</v>
       </c>
       <c r="V25" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W25" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X25" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="Y25">
         <v>24</v>
       </c>
+      <c r="Z25">
+        <v>24</v>
+      </c>
       <c r="AC25" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF25" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH25" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI25" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM25">
+        <v>1.74</v>
+      </c>
+      <c r="AN25">
+        <v>16.4245740964042</v>
+      </c>
+      <c r="AR25">
+        <v>0.54</v>
+      </c>
+      <c r="AS25">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="AT25">
+        <v>0.91</v>
+      </c>
+      <c r="AU25">
+        <v>4.18</v>
+      </c>
+      <c r="BD25">
+        <v>5.66</v>
+      </c>
+      <c r="BE25">
+        <v>7.27</v>
+      </c>
+      <c r="BF25">
+        <v>11.0731902988657</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26">
-        <v>-52.087986639999983</v>
+        <v>-52.087986639999997</v>
       </c>
       <c r="C26">
         <v>-22.252054730000001</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G26" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2901,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O26">
         <v>120218</v>
@@ -2919,57 +3691,90 @@
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W26" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X26" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="Y26">
         <v>25</v>
       </c>
+      <c r="Z26">
+        <v>25</v>
+      </c>
       <c r="AC26" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE26" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF26" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH26" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI26" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM26">
+        <v>1.71</v>
+      </c>
+      <c r="AN26">
+        <v>7.4421049376990398</v>
+      </c>
+      <c r="AR26">
+        <v>0.93</v>
+      </c>
+      <c r="AS26">
+        <v>6.63</v>
+      </c>
+      <c r="AT26">
+        <v>1.22</v>
+      </c>
+      <c r="AU26">
+        <v>4.03</v>
+      </c>
+      <c r="BB26">
+        <v>9.0093761427352597</v>
+      </c>
+      <c r="BD26">
+        <v>5.56</v>
+      </c>
+      <c r="BE26">
+        <v>7.31</v>
+      </c>
+      <c r="BF26">
+        <v>10.6161762417528</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
       <c r="B27">
-        <v>-52.087986639999983</v>
+        <v>-52.087986639999997</v>
       </c>
       <c r="C27">
         <v>-22.252054730000001</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2981,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O27">
         <v>120218</v>
@@ -2999,57 +3804,90 @@
         <v>2</v>
       </c>
       <c r="V27" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W27" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X27" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="Y27">
         <v>26</v>
       </c>
+      <c r="Z27">
+        <v>26</v>
+      </c>
       <c r="AC27" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE27" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF27" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH27" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI27" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM27">
+        <v>1.5</v>
+      </c>
+      <c r="AN27">
+        <v>4.447948551464</v>
+      </c>
+      <c r="AR27">
+        <v>1.78</v>
+      </c>
+      <c r="AS27">
+        <v>6.2</v>
+      </c>
+      <c r="AT27">
+        <v>1.06</v>
+      </c>
+      <c r="AU27">
+        <v>3.13</v>
+      </c>
+      <c r="BB27">
+        <v>7.9230325209195698</v>
+      </c>
+      <c r="BD27">
+        <v>5.5</v>
+      </c>
+      <c r="BE27">
+        <v>7.24</v>
+      </c>
+      <c r="BF27">
+        <v>11.4288161488497</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
       <c r="B28">
-        <v>-52.090599349999977</v>
+        <v>-52.090599349999998</v>
       </c>
       <c r="C28">
         <v>-22.25646528</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G28" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -3061,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O28">
         <v>120218</v>
@@ -3079,57 +3917,90 @@
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W28" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="Y28">
         <v>27</v>
       </c>
+      <c r="Z28">
+        <v>27</v>
+      </c>
       <c r="AC28" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE28" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF28" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH28" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI28" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM28">
+        <v>3</v>
+      </c>
+      <c r="AN28">
+        <v>9.2718671737315699</v>
+      </c>
+      <c r="AR28">
+        <v>1.98</v>
+      </c>
+      <c r="AS28">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="AT28">
+        <v>1.25</v>
+      </c>
+      <c r="AU28">
+        <v>3.33</v>
+      </c>
+      <c r="BB28">
+        <v>9.9146624942483292</v>
+      </c>
+      <c r="BD28">
+        <v>4.55</v>
+      </c>
+      <c r="BE28">
+        <v>6.77</v>
+      </c>
+      <c r="BF28">
+        <v>18.7534343019279</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>24</v>
       </c>
       <c r="B29">
-        <v>-52.090599349999977</v>
+        <v>-52.090599349999998</v>
       </c>
       <c r="C29">
         <v>-22.25646528</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -3141,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O29">
         <v>120218</v>
@@ -3159,54 +4030,84 @@
         <v>2</v>
       </c>
       <c r="V29" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W29" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X29" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="Y29">
         <v>28</v>
       </c>
+      <c r="Z29">
+        <v>28</v>
+      </c>
       <c r="AC29" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF29" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH29" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI29" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM29">
+        <v>3.88</v>
+      </c>
+      <c r="AN29">
+        <v>4.9469746158365</v>
+      </c>
+      <c r="AR29">
+        <v>2.88</v>
+      </c>
+      <c r="AS29">
+        <v>2.81</v>
+      </c>
+      <c r="AT29">
+        <v>1.41</v>
+      </c>
+      <c r="AU29">
+        <v>1.17</v>
+      </c>
+      <c r="BD29">
+        <v>4.24</v>
+      </c>
+      <c r="BE29">
+        <v>6.72</v>
+      </c>
+      <c r="BF29">
+        <v>19.767949190915498</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25</v>
       </c>
       <c r="B30">
-        <v>-52.085268769999978</v>
+        <v>-52.085268769999999</v>
       </c>
       <c r="C30">
-        <v>-22.256198069999972</v>
+        <v>-22.25619807</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3218,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O30">
         <v>120218</v>
@@ -3236,54 +4137,84 @@
         <v>1</v>
       </c>
       <c r="V30" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W30" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X30" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Y30">
         <v>29</v>
       </c>
+      <c r="Z30">
+        <v>29</v>
+      </c>
       <c r="AC30" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF30" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH30" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI30" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM30">
+        <v>2.06</v>
+      </c>
+      <c r="AN30">
+        <v>21.913860804501802</v>
+      </c>
+      <c r="AR30">
+        <v>0.26</v>
+      </c>
+      <c r="AS30">
+        <v>6.86</v>
+      </c>
+      <c r="AT30">
+        <v>1.35</v>
+      </c>
+      <c r="AU30">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="BD30">
+        <v>5.19</v>
+      </c>
+      <c r="BE30">
+        <v>7.08</v>
+      </c>
+      <c r="BF30">
+        <v>13.527570990868201</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>25</v>
       </c>
       <c r="B31">
-        <v>-52.085268769999978</v>
+        <v>-52.085268769999999</v>
       </c>
       <c r="C31">
-        <v>-22.256198069999972</v>
+        <v>-22.25619807</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3295,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O31">
         <v>120218</v>
@@ -3313,54 +4244,84 @@
         <v>2</v>
       </c>
       <c r="V31" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W31" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X31" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Y31">
         <v>30</v>
       </c>
+      <c r="Z31">
+        <v>30</v>
+      </c>
       <c r="AC31" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF31" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH31" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI31" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM31">
+        <v>2.94</v>
+      </c>
+      <c r="AN31">
+        <v>6.2777107874965203</v>
+      </c>
+      <c r="AR31">
+        <v>1.68</v>
+      </c>
+      <c r="AS31">
+        <v>3.96</v>
+      </c>
+      <c r="AT31">
+        <v>1.36</v>
+      </c>
+      <c r="AU31">
+        <v>1.81</v>
+      </c>
+      <c r="BD31">
+        <v>4.43</v>
+      </c>
+      <c r="BE31">
+        <v>6.89</v>
+      </c>
+      <c r="BF31">
+        <v>16.5259669502585</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26</v>
       </c>
       <c r="B32">
-        <v>-52.085586140000018</v>
+        <v>-52.085586139999997</v>
       </c>
       <c r="C32">
-        <v>-22.259396189999979</v>
+        <v>-22.25939619</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3372,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O32">
         <v>120218</v>
@@ -3390,54 +4351,84 @@
         <v>1</v>
       </c>
       <c r="V32" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W32" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X32" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="Y32">
         <v>31</v>
       </c>
+      <c r="Z32">
+        <v>31</v>
+      </c>
       <c r="AC32" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF32" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH32" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI32" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM32">
+        <v>2.65</v>
+      </c>
+      <c r="AN32">
+        <v>19.7514145255542</v>
+      </c>
+      <c r="AR32">
+        <v>0.05</v>
+      </c>
+      <c r="AS32">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="AT32">
+        <v>1.82</v>
+      </c>
+      <c r="AU32">
+        <v>7.6</v>
+      </c>
+      <c r="BD32">
+        <v>5.93</v>
+      </c>
+      <c r="BE32">
+        <v>7.21</v>
+      </c>
+      <c r="BF32">
+        <v>11.795863255198199</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26</v>
       </c>
       <c r="B33">
-        <v>-52.085586140000018</v>
+        <v>-52.085586139999997</v>
       </c>
       <c r="C33">
-        <v>-22.259396189999979</v>
+        <v>-22.25939619</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3449,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O33">
         <v>120218</v>
@@ -3467,54 +4458,84 @@
         <v>2</v>
       </c>
       <c r="V33" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W33" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X33" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="Y33">
         <v>32</v>
       </c>
+      <c r="Z33">
+        <v>32</v>
+      </c>
       <c r="AC33" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF33" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH33" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI33" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM33">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AN33">
+        <v>8.6064990879015593</v>
+      </c>
+      <c r="AR33">
+        <v>0.09</v>
+      </c>
+      <c r="AS33">
+        <v>11.29</v>
+      </c>
+      <c r="AT33">
+        <v>1.5</v>
+      </c>
+      <c r="AU33">
+        <v>5.01</v>
+      </c>
+      <c r="BD33">
+        <v>5.5</v>
+      </c>
+      <c r="BE33">
+        <v>7.19</v>
+      </c>
+      <c r="BF33">
+        <v>12.0470871257724</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>27</v>
       </c>
       <c r="B34">
-        <v>-52.082672489999958</v>
+        <v>-52.08267249</v>
       </c>
       <c r="C34">
-        <v>-22.261961029999991</v>
+        <v>-22.261961029999998</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3526,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O34">
         <v>120218</v>
@@ -3544,57 +4565,90 @@
         <v>1</v>
       </c>
       <c r="V34" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W34" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X34" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Y34">
         <v>33</v>
       </c>
+      <c r="Z34">
+        <v>33</v>
+      </c>
       <c r="AC34" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE34" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF34" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH34" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI34" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM34">
+        <v>2.44</v>
+      </c>
+      <c r="AN34">
+        <v>6.4440528089540301</v>
+      </c>
+      <c r="AR34">
+        <v>0.09</v>
+      </c>
+      <c r="AS34">
+        <v>37.76</v>
+      </c>
+      <c r="AT34">
+        <v>4.91</v>
+      </c>
+      <c r="AU34">
+        <v>20.23</v>
+      </c>
+      <c r="BB34">
+        <v>16.0706096845372</v>
+      </c>
+      <c r="BD34">
+        <v>5.59</v>
+      </c>
+      <c r="BE34">
+        <v>6.85</v>
+      </c>
+      <c r="BF34">
+        <v>17.2373906334814</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>27</v>
       </c>
       <c r="B35">
-        <v>-52.082672489999958</v>
+        <v>-52.08267249</v>
       </c>
       <c r="C35">
-        <v>-22.261961029999991</v>
+        <v>-22.261961029999998</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3606,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O35">
         <v>120218</v>
@@ -3624,54 +4678,84 @@
         <v>2</v>
       </c>
       <c r="V35" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W35" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X35" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="Y35">
         <v>34</v>
       </c>
+      <c r="Z35">
+        <v>34</v>
+      </c>
       <c r="AC35" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF35" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH35" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI35" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM35">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="AN35">
+        <v>6.7767368518690301</v>
+      </c>
+      <c r="AR35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AS35">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="AT35">
+        <v>4.95</v>
+      </c>
+      <c r="AU35">
+        <v>18.38</v>
+      </c>
+      <c r="BD35">
+        <v>5.59</v>
+      </c>
+      <c r="BE35">
+        <v>6.81</v>
+      </c>
+      <c r="BF35">
+        <v>17.9794402799882</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>18</v>
       </c>
       <c r="B36">
-        <v>-52.102899439999987</v>
+        <v>-52.102899440000002</v>
       </c>
       <c r="C36">
-        <v>-22.484717329999981</v>
+        <v>-22.484717329999999</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3683,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O36">
         <v>120053</v>
@@ -3701,57 +4785,90 @@
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W36" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X36" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="Y36">
         <v>35</v>
       </c>
+      <c r="Z36">
+        <v>35</v>
+      </c>
       <c r="AC36" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE36" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF36" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH36" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI36" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM36">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AN36">
+        <v>13.097733667254101</v>
+      </c>
+      <c r="AR36">
+        <v>0.04</v>
+      </c>
+      <c r="AS36">
+        <v>26.99</v>
+      </c>
+      <c r="AT36">
+        <v>3.16</v>
+      </c>
+      <c r="AU36">
+        <v>5.57</v>
+      </c>
+      <c r="BB36">
+        <v>13.173693359695401</v>
+      </c>
+      <c r="BD36">
+        <v>6.74</v>
+      </c>
+      <c r="BE36">
+        <v>7.6</v>
+      </c>
+      <c r="BF36">
+        <v>7.8209489665318204</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>18</v>
       </c>
       <c r="B37">
-        <v>-52.102899439999987</v>
+        <v>-52.102899440000002</v>
       </c>
       <c r="C37">
-        <v>-22.484717329999981</v>
+        <v>-22.484717329999999</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="G37" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3763,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O37">
         <v>120053</v>
@@ -3781,57 +4898,90 @@
         <v>2</v>
       </c>
       <c r="V37" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W37" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y37">
         <v>36</v>
       </c>
+      <c r="Z37">
+        <v>36</v>
+      </c>
       <c r="AC37" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE37" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF37" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH37" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI37" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM37">
+        <v>2.99</v>
+      </c>
+      <c r="AN37">
+        <v>10.103577281019099</v>
+      </c>
+      <c r="AR37">
+        <v>0.05</v>
+      </c>
+      <c r="AS37">
+        <v>14.35</v>
+      </c>
+      <c r="AT37">
+        <v>3.58</v>
+      </c>
+      <c r="AU37">
+        <v>4.18</v>
+      </c>
+      <c r="BB37">
+        <v>10.457834305156201</v>
+      </c>
+      <c r="BD37">
+        <v>6.52</v>
+      </c>
+      <c r="BE37">
+        <v>7.49</v>
+      </c>
+      <c r="BF37">
+        <v>8.7820766344737908</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>19</v>
       </c>
       <c r="B38">
-        <v>-52.429023062443427</v>
+        <v>-52.429023062443399</v>
       </c>
       <c r="C38">
-        <v>-22.23579774534474</v>
+        <v>-22.235797745344701</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G38" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -3843,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O38">
         <v>120418</v>
@@ -3861,57 +5011,90 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W38" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Y38">
         <v>37</v>
       </c>
+      <c r="Z38">
+        <v>37</v>
+      </c>
       <c r="AC38" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE38" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF38" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH38" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI38" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM38">
+        <v>1.41</v>
+      </c>
+      <c r="AN38">
+        <v>5.6123427016665097</v>
+      </c>
+      <c r="AR38">
+        <v>0.06</v>
+      </c>
+      <c r="AS38">
+        <v>8.92</v>
+      </c>
+      <c r="AT38">
+        <v>0.98</v>
+      </c>
+      <c r="AU38">
+        <v>4.99</v>
+      </c>
+      <c r="BB38">
+        <v>9.5525479536430993</v>
+      </c>
+      <c r="BD38">
+        <v>5.43</v>
+      </c>
+      <c r="BE38">
+        <v>7.26</v>
+      </c>
+      <c r="BF38">
+        <v>11.190485388972199</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>19</v>
       </c>
       <c r="B39">
-        <v>-52.429023062443427</v>
+        <v>-52.429023062443399</v>
       </c>
       <c r="C39">
-        <v>-22.23579774534474</v>
+        <v>-22.235797745344701</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F39" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G39" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -3923,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O39">
         <v>120418</v>
@@ -3941,57 +5124,90 @@
         <v>2</v>
       </c>
       <c r="V39" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W39" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Y39">
         <v>38</v>
       </c>
+      <c r="Z39">
+        <v>38</v>
+      </c>
       <c r="AC39" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE39" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF39" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH39" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI39" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM39">
+        <v>1.64</v>
+      </c>
+      <c r="AN39">
+        <v>4.780632594379</v>
+      </c>
+      <c r="AR39">
+        <v>0.06</v>
+      </c>
+      <c r="AS39">
+        <v>7.46</v>
+      </c>
+      <c r="AT39">
+        <v>0.5</v>
+      </c>
+      <c r="AU39">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="BB39">
+        <v>7.5609179803143496</v>
+      </c>
+      <c r="BD39">
+        <v>5.25</v>
+      </c>
+      <c r="BE39">
+        <v>7.17</v>
+      </c>
+      <c r="BF39">
+        <v>12.303661468099399</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>20</v>
       </c>
       <c r="B40">
-        <v>-52.426248440509262</v>
+        <v>-52.426248440509298</v>
       </c>
       <c r="C40">
-        <v>-22.233082158038879</v>
+        <v>-22.233082158038901</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G40" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -4003,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O40">
         <v>120418</v>
@@ -4021,57 +5237,90 @@
         <v>1</v>
       </c>
       <c r="V40" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W40" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y40">
         <v>39</v>
       </c>
+      <c r="Z40">
+        <v>39</v>
+      </c>
       <c r="AC40" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AE40" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF40" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH40" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI40" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM40">
+        <v>1.89</v>
+      </c>
+      <c r="AN40">
+        <v>4.9469746158365</v>
+      </c>
+      <c r="AR40">
+        <v>0.08</v>
+      </c>
+      <c r="AS40">
+        <v>7.66</v>
+      </c>
+      <c r="AT40">
+        <v>0.41</v>
+      </c>
+      <c r="AU40">
+        <v>5.01</v>
+      </c>
+      <c r="BB40">
+        <v>7.5609179803143496</v>
+      </c>
+      <c r="BD40">
+        <v>5.52</v>
+      </c>
+      <c r="BE40">
+        <v>7.31</v>
+      </c>
+      <c r="BF40">
+        <v>10.6161762417528</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20</v>
       </c>
       <c r="B41">
-        <v>-52.426248440509262</v>
+        <v>-52.426248440509298</v>
       </c>
       <c r="C41">
-        <v>-22.233082158038879</v>
+        <v>-22.233082158038901</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -4083,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O41">
         <v>120418</v>
@@ -4101,54 +5350,84 @@
         <v>2</v>
       </c>
       <c r="V41" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W41" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y41">
         <v>40</v>
       </c>
+      <c r="Z41">
+        <v>40</v>
+      </c>
       <c r="AC41" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF41" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH41" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI41" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM41">
+        <v>1.52</v>
+      </c>
+      <c r="AN41">
+        <v>5.9450267445815204</v>
+      </c>
+      <c r="AR41">
+        <v>0.03</v>
+      </c>
+      <c r="AS41">
+        <v>9.98</v>
+      </c>
+      <c r="AT41">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AU41">
+        <v>5.12</v>
+      </c>
+      <c r="BD41">
+        <v>5.43</v>
+      </c>
+      <c r="BE41">
+        <v>7.26</v>
+      </c>
+      <c r="BF41">
+        <v>11.190485388972199</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>21</v>
       </c>
       <c r="B42">
-        <v>-52.42332623211265</v>
+        <v>-52.4233262321127</v>
       </c>
       <c r="C42">
-        <v>-22.229864777077012</v>
+        <v>-22.229864777077001</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G42" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -4160,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O42">
         <v>120418</v>
@@ -4178,10 +5457,10 @@
         <v>1</v>
       </c>
       <c r="V42" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W42" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X42" t="s">
         <v>129</v>
@@ -4189,43 +5468,73 @@
       <c r="Y42">
         <v>41</v>
       </c>
+      <c r="Z42">
+        <v>41</v>
+      </c>
       <c r="AC42" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF42" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH42" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI42" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM42">
+        <v>1.57</v>
+      </c>
+      <c r="AN42">
+        <v>10.2699193024766</v>
+      </c>
+      <c r="AR42">
+        <v>0.08</v>
+      </c>
+      <c r="AS42">
+        <v>6.54</v>
+      </c>
+      <c r="AT42">
+        <v>0.39</v>
+      </c>
+      <c r="AU42">
+        <v>3.35</v>
+      </c>
+      <c r="BD42">
+        <v>5.05</v>
+      </c>
+      <c r="BE42">
+        <v>7.22</v>
+      </c>
+      <c r="BF42">
+        <v>11.6722227878449</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>21</v>
       </c>
       <c r="B43">
-        <v>-52.42332623211265</v>
+        <v>-52.4233262321127</v>
       </c>
       <c r="C43">
-        <v>-22.229864777077012</v>
+        <v>-22.229864777077001</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G43" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -4237,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O43">
         <v>120418</v>
@@ -4255,10 +5564,10 @@
         <v>2</v>
       </c>
       <c r="V43" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W43" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X43" t="s">
         <v>130</v>
@@ -4266,43 +5575,73 @@
       <c r="Y43">
         <v>42</v>
       </c>
+      <c r="Z43">
+        <v>42</v>
+      </c>
       <c r="AC43" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF43" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH43" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI43" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM43">
+        <v>1.71</v>
+      </c>
+      <c r="AN43">
+        <v>5.4460006802090097</v>
+      </c>
+      <c r="AR43">
+        <v>0.05</v>
+      </c>
+      <c r="AS43">
+        <v>6.17</v>
+      </c>
+      <c r="AT43">
+        <v>0.33</v>
+      </c>
+      <c r="AU43">
+        <v>4.09</v>
+      </c>
+      <c r="BD43">
+        <v>5.33</v>
+      </c>
+      <c r="BE43">
+        <v>7.36</v>
+      </c>
+      <c r="BF43">
+        <v>10.0713413295747</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>22</v>
       </c>
       <c r="B44">
-        <v>-52.420536851370521</v>
+        <v>-52.4205368513705</v>
       </c>
       <c r="C44">
-        <v>-22.226898292795671</v>
+        <v>-22.226898292795699</v>
       </c>
       <c r="D44" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -4314,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O44">
         <v>120418</v>
@@ -4332,54 +5671,84 @@
         <v>1</v>
       </c>
       <c r="V44" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="W44" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Y44">
         <v>43</v>
       </c>
+      <c r="Z44">
+        <v>43</v>
+      </c>
       <c r="AC44" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF44" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH44" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI44" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM44">
+        <v>1.39</v>
+      </c>
+      <c r="AN44">
+        <v>6.1113687660390204</v>
+      </c>
+      <c r="AR44">
+        <v>0.15</v>
+      </c>
+      <c r="AS44">
+        <v>5.81</v>
+      </c>
+      <c r="AT44">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AU44">
+        <v>3.38</v>
+      </c>
+      <c r="BD44">
+        <v>4.8</v>
+      </c>
+      <c r="BE44">
+        <v>7.1</v>
+      </c>
+      <c r="BF44">
+        <v>13.245473857485299</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>22</v>
       </c>
       <c r="B45">
-        <v>-52.420536851370521</v>
+        <v>-52.4205368513705</v>
       </c>
       <c r="C45">
-        <v>-22.226898292795671</v>
+        <v>-22.226898292795699</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -4391,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="O45">
         <v>120418</v>
@@ -4409,31 +5778,63 @@
         <v>2</v>
       </c>
       <c r="V45" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="W45" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="X45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y45">
         <v>44</v>
       </c>
+      <c r="Z45">
+        <v>44</v>
+      </c>
       <c r="AC45" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AF45" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AH45" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="AI45" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="AM45">
+        <v>1.9</v>
+      </c>
+      <c r="AN45">
+        <v>5.4460006802090097</v>
+      </c>
+      <c r="AR45">
+        <v>0.87</v>
+      </c>
+      <c r="AS45">
+        <v>4.57</v>
+      </c>
+      <c r="AT45">
+        <v>0.67</v>
+      </c>
+      <c r="AU45">
+        <v>3.22</v>
+      </c>
+      <c r="BD45">
+        <v>4.53</v>
+      </c>
+      <c r="BE45">
+        <v>7.06</v>
+      </c>
+      <c r="BF45">
+        <v>13.8156761231734</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:BI45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>